--- a/src/evaluation/data/processed/RES_main_model.xlsx
+++ b/src/evaluation/data/processed/RES_main_model.xlsx
@@ -472,19 +472,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.466</v>
+        <v>16.096</v>
       </c>
       <c r="C2" t="n">
         <v>12.08</v>
       </c>
       <c r="D2" t="n">
-        <v>28.85</v>
+        <v>27.478</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7271686884870679</v>
+        <v>0.8419385492556223</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2752613240418119</v>
+        <v>0.3059051306873185</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -497,19 +497,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.112</v>
+        <v>10.78</v>
       </c>
       <c r="C3" t="n">
         <v>10.01</v>
       </c>
       <c r="D3" t="n">
-        <v>18.57</v>
+        <v>16.674</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09494773519163763</v>
+        <v>0.1055179090029041</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -531,13 +531,13 @@
         <v>23.792</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1483176928358891</v>
+        <v>0.2578397212543551</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5079766536964979</v>
+        <v>0.658830062939652</v>
       </c>
     </row>
     <row r="5">
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.352</v>
+        <v>17.094</v>
       </c>
       <c r="C5" t="n">
         <v>15.68</v>
       </c>
       <c r="D5" t="n">
-        <v>25.656</v>
+        <v>27.038</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4852368963149462</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5888501742160279</v>
+        <v>0.6544046466602129</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6892996108949416</v>
+        <v>0.9592743428359869</v>
       </c>
     </row>
     <row r="6">
@@ -572,22 +572,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.96</v>
+        <v>16.094</v>
       </c>
       <c r="C6" t="n">
-        <v>19.98</v>
+        <v>19.25</v>
       </c>
       <c r="D6" t="n">
-        <v>25.286</v>
+        <v>21.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8981460288395513</v>
+        <v>0.841621792841305</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9634146341463417</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6533073929961092</v>
+        <v>0.4837097371343946</v>
       </c>
     </row>
     <row r="7">
@@ -597,22 +597,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.85</v>
+        <v>13.304</v>
       </c>
       <c r="C7" t="n">
-        <v>20.4</v>
+        <v>12.1</v>
       </c>
       <c r="D7" t="n">
-        <v>27.488</v>
+        <v>17.682</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0.3997465948685457</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.3078412391093901</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8675097276264593</v>
+        <v>0.09329877823028501</v>
       </c>
     </row>
   </sheetData>
